--- a/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_15_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem4_Bullseye5/Res/Comparativa_15_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.185631</v>
+        <v>0.182659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -598,25 +598,25 @@
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.59915</v>
+        <v>0.60119</v>
       </c>
       <c r="H2" t="n">
-        <v>0.663009</v>
+        <v>0.633229</v>
       </c>
       <c r="I2" t="n">
-        <v>0.629464</v>
+        <v>0.616794</v>
       </c>
       <c r="J2" t="n">
-        <v>0.185722</v>
+        <v>0.183091</v>
       </c>
       <c r="K2" t="n">
-        <v>0.601124</v>
+        <v>0.615819</v>
       </c>
       <c r="L2" t="n">
-        <v>0.629412</v>
+        <v>0.641176</v>
       </c>
       <c r="M2" t="n">
-        <v>0.614943</v>
+        <v>0.628242</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_5.txt</t>
+          <t>_2_15_1_1790732256_2.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.239748</v>
+        <v>0.23974</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.245063</v>
+        <v>0.245068</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_3.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_18.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +876,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.239749</v>
+        <v>0.239748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.245065</v>
+        <v>0.245086</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_12.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_11.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -969,35 +969,43 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.239749</v>
+        <v>0.185155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E6" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0.594444</v>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.6708460000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.630339</v>
+      </c>
       <c r="J6" t="n">
-        <v>0.245069</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0.185172</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.608696</v>
+      </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>0.658824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.632768</v>
+      </c>
       <c r="N6" t="n">
         <v>0.2</v>
       </c>
@@ -1032,23 +1040,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_10.txt</t>
+          <t>_2_15_1_1790732256_6.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>15</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1062,35 +1070,43 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.23975</v>
+        <v>0.195193</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E7" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0.502667</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>0.590909</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.543228</v>
+      </c>
       <c r="J7" t="n">
-        <v>0.245058</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0.194372</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.527778</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>0.558824</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.542857</v>
+      </c>
       <c r="N7" t="n">
         <v>0.2</v>
       </c>
@@ -1125,23 +1141,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_17.txt</t>
+          <t>_2_15_1_1790732256_17.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1155,7 +1171,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.239748</v>
+        <v>0.239749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1177,7 +1193,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.245051</v>
+        <v>0.245069</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_15.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_10.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1248,43 +1264,35 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.185852</v>
+        <v>0.239748</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F9" t="n">
         <v>200000</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.573748</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.664577</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.615832</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.187112</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5786520000000001</v>
-      </c>
+        <v>0.245063</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.605882</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.591954</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0.2</v>
       </c>
@@ -1319,23 +1327,23 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_18.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_3.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z9" t="n">
         <v>15</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1349,43 +1357,35 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.180415</v>
+        <v>0.239752</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.556944</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.6285269999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.590574</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.179453</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.586021</v>
-      </c>
+        <v>0.245069</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.641176</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.61236</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>0.2</v>
       </c>
@@ -1420,23 +1420,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_0.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_7.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
       </c>
       <c r="AA10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.182659</v>
+        <v>0.17471</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1467,25 +1467,25 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.60119</v>
+        <v>0.609329</v>
       </c>
       <c r="H11" t="n">
-        <v>0.633229</v>
+        <v>0.655172</v>
       </c>
       <c r="I11" t="n">
-        <v>0.616794</v>
+        <v>0.63142</v>
       </c>
       <c r="J11" t="n">
-        <v>0.183091</v>
+        <v>0.175358</v>
       </c>
       <c r="K11" t="n">
-        <v>0.615819</v>
+        <v>0.604938</v>
       </c>
       <c r="L11" t="n">
-        <v>0.641176</v>
+        <v>0.576471</v>
       </c>
       <c r="M11" t="n">
-        <v>0.628242</v>
+        <v>0.590361</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_2.txt</t>
+          <t>_2_15_1_1790732256_9.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1551,7 +1551,7 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.239747</v>
+        <v>0.239746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.245068</v>
+        <v>0.245066</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_14.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_19.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.245079</v>
+        <v>0.245068</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_14.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1737,7 +1737,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.239748</v>
+        <v>0.239747</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.245086</v>
+        <v>0.245064</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_11.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_6.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1830,43 +1830,35 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.182819</v>
+        <v>0.239747</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.610698</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.644201</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6270019999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.184882</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.60355</v>
-      </c>
+        <v>0.245054</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.60177</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0.2</v>
       </c>
@@ -1901,23 +1893,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_7.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_1.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
       </c>
       <c r="AA15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1931,7 +1923,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.182103</v>
+        <v>0.184474</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1948,25 +1940,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.58616</v>
+        <v>0.578729</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6771160000000001</v>
+        <v>0.65674</v>
       </c>
       <c r="I16" t="n">
-        <v>0.628364</v>
+        <v>0.615272</v>
       </c>
       <c r="J16" t="n">
-        <v>0.181111</v>
+        <v>0.185581</v>
       </c>
       <c r="K16" t="n">
-        <v>0.603261</v>
+        <v>0.594595</v>
       </c>
       <c r="L16" t="n">
-        <v>0.652941</v>
+        <v>0.6470590000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.627119</v>
+        <v>0.619718</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2002,7 +1994,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_14.txt</t>
+          <t>_2_15_1_1790732256_15.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2125,7 +2117,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.195193</v>
+        <v>0.188827</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2142,25 +2134,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.502667</v>
+        <v>0.593838</v>
       </c>
       <c r="H18" t="n">
-        <v>0.590909</v>
+        <v>0.664577</v>
       </c>
       <c r="I18" t="n">
-        <v>0.543228</v>
+        <v>0.627219</v>
       </c>
       <c r="J18" t="n">
-        <v>0.194372</v>
+        <v>0.187661</v>
       </c>
       <c r="K18" t="n">
-        <v>0.527778</v>
+        <v>0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.558824</v>
+        <v>0.635294</v>
       </c>
       <c r="M18" t="n">
-        <v>0.542857</v>
+        <v>0.617143</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2196,7 +2188,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_17.txt</t>
+          <t>_2_15_1_1790732256_4.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2226,43 +2218,35 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.174776</v>
+        <v>0.23975</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.6354880000000001</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.7241379999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.6769230000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.171428</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.67033</v>
-      </c>
+        <v>0.245058</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.717647</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.693182</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0.2</v>
       </c>
@@ -2297,23 +2281,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_12.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_17.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>15</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2327,7 +2311,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.189742</v>
+        <v>0.185852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2344,25 +2328,25 @@
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.594828</v>
+        <v>0.573748</v>
       </c>
       <c r="H20" t="n">
-        <v>0.648903</v>
+        <v>0.664577</v>
       </c>
       <c r="I20" t="n">
-        <v>0.62069</v>
+        <v>0.615832</v>
       </c>
       <c r="J20" t="n">
-        <v>0.189614</v>
+        <v>0.187112</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5988019999999999</v>
+        <v>0.5786520000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.588235</v>
+        <v>0.605882</v>
       </c>
       <c r="M20" t="n">
-        <v>0.593472</v>
+        <v>0.591954</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2398,7 +2382,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_10.txt</t>
+          <t>_2_15_1_1790732256_18.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2521,7 +2505,7 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.239746</v>
+        <v>0.239749</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2543,7 +2527,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.245066</v>
+        <v>0.245065</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
@@ -2584,7 +2568,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_19.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_12.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2614,7 +2598,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.17471</v>
+        <v>0.174776</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2631,25 +2615,25 @@
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.609329</v>
+        <v>0.6354880000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.655172</v>
+        <v>0.7241379999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.63142</v>
+        <v>0.6769230000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.175358</v>
+        <v>0.171428</v>
       </c>
       <c r="K23" t="n">
-        <v>0.604938</v>
+        <v>0.67033</v>
       </c>
       <c r="L23" t="n">
-        <v>0.576471</v>
+        <v>0.717647</v>
       </c>
       <c r="M23" t="n">
-        <v>0.590361</v>
+        <v>0.693182</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2685,7 +2669,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_9.txt</t>
+          <t>_2_15_1_1790732256_12.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2715,35 +2699,43 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.239752</v>
+        <v>0.182819</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E24" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0.610698</v>
+      </c>
       <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>0.644201</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6270019999999999</v>
+      </c>
       <c r="J24" t="n">
-        <v>0.245069</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>0.184882</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.60355</v>
+      </c>
       <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.60177</v>
+      </c>
       <c r="N24" t="n">
         <v>0.2</v>
       </c>
@@ -2778,23 +2770,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_7.txt</t>
+          <t>_2_15_1_1790732256_7.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>15</v>
       </c>
       <c r="AA24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2808,7 +2800,7 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.185155</v>
+        <v>0.186421</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2825,25 +2817,25 @@
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.594444</v>
+        <v>0.57975</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6708460000000001</v>
+        <v>0.655172</v>
       </c>
       <c r="I25" t="n">
-        <v>0.630339</v>
+        <v>0.615158</v>
       </c>
       <c r="J25" t="n">
-        <v>0.185172</v>
+        <v>0.187781</v>
       </c>
       <c r="K25" t="n">
-        <v>0.608696</v>
+        <v>0.5672509999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.658824</v>
+        <v>0.570588</v>
       </c>
       <c r="M25" t="n">
-        <v>0.632768</v>
+        <v>0.5689149999999999</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2879,7 +2871,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_6.txt</t>
+          <t>_2_15_1_1790732256_1.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -2909,35 +2901,43 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.239747</v>
+        <v>0.185631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E26" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0.59915</v>
+      </c>
       <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>0.663009</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.629464</v>
+      </c>
       <c r="J26" t="n">
-        <v>0.245054</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
+        <v>0.185722</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.601124</v>
+      </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
+        <v>0.629412</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.614943</v>
+      </c>
       <c r="N26" t="n">
         <v>0.2</v>
       </c>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_1.txt</t>
+          <t>_2_15_1_1790732256_5.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>15</v>
       </c>
       <c r="AA26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3002,35 +3002,43 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.239747</v>
+        <v>0.174243</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E27" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
         <v>200000</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>0.615932</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>0.678683</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.645787</v>
+      </c>
       <c r="J27" t="n">
-        <v>0.245069</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>0.171653</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.648352</v>
+      </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
+        <v>0.694118</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.670455</v>
+      </c>
       <c r="N27" t="n">
         <v>0.2</v>
       </c>
@@ -3065,23 +3073,23 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_8.txt</t>
+          <t>_2_15_1_1790732256_19.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z27" t="n">
         <v>15</v>
       </c>
       <c r="AA27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3095,7 +3103,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.23975</v>
+        <v>0.239748</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3117,7 +3125,7 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0.245067</v>
+        <v>0.245051</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
@@ -3158,7 +3166,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_0.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_15.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3188,35 +3196,43 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.239747</v>
+        <v>0.180415</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E29" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0.556944</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>0.6285269999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.590574</v>
+      </c>
       <c r="J29" t="n">
-        <v>0.245062</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>0.179453</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.586021</v>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>0.641176</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.61236</v>
+      </c>
       <c r="N29" t="n">
         <v>0.2</v>
       </c>
@@ -3251,23 +3267,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_13.txt</t>
+          <t>_2_15_1_1790732256_0.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3281,7 +3297,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.186589</v>
+        <v>0.182341</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3298,25 +3314,25 @@
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.599338</v>
+        <v>0.596467</v>
       </c>
       <c r="H30" t="n">
-        <v>0.567398</v>
+        <v>0.688088</v>
       </c>
       <c r="I30" t="n">
-        <v>0.582931</v>
+        <v>0.63901</v>
       </c>
       <c r="J30" t="n">
-        <v>0.184527</v>
+        <v>0.181189</v>
       </c>
       <c r="K30" t="n">
-        <v>0.605442</v>
+        <v>0.615789</v>
       </c>
       <c r="L30" t="n">
-        <v>0.523529</v>
+        <v>0.688235</v>
       </c>
       <c r="M30" t="n">
-        <v>0.561514</v>
+        <v>0.65</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3352,7 +3368,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_3.txt</t>
+          <t>_2_15_1_1790732256_16.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3483,7 +3499,7 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.174243</v>
+        <v>0.182103</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3500,25 +3516,25 @@
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.615932</v>
+        <v>0.58616</v>
       </c>
       <c r="H32" t="n">
-        <v>0.678683</v>
+        <v>0.6771160000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.645787</v>
+        <v>0.628364</v>
       </c>
       <c r="J32" t="n">
-        <v>0.171653</v>
+        <v>0.181111</v>
       </c>
       <c r="K32" t="n">
-        <v>0.648352</v>
+        <v>0.603261</v>
       </c>
       <c r="L32" t="n">
-        <v>0.694118</v>
+        <v>0.652941</v>
       </c>
       <c r="M32" t="n">
-        <v>0.670455</v>
+        <v>0.627119</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3554,7 +3570,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_19.txt</t>
+          <t>_2_15_1_1790732256_14.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3584,43 +3600,35 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.182341</v>
+        <v>0.239747</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E33" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
-      <c r="G33" t="n">
-        <v>0.596467</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.688088</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.63901</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>0.181189</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.615789</v>
-      </c>
+        <v>0.245069</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>0.688235</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>0.2</v>
       </c>
@@ -3655,23 +3663,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_16.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_8.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>15</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3685,43 +3693,35 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.182785</v>
+        <v>0.23975</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F34" t="n">
         <v>200000</v>
       </c>
-      <c r="G34" t="n">
-        <v>0.59584</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.6285269999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.611747</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.183844</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.601156</v>
-      </c>
+        <v>0.245048</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>0.611765</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.606414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>0.2</v>
       </c>
@@ -3756,23 +3756,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_8.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_9.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z34" t="n">
         <v>15</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -3786,7 +3786,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.23975</v>
+        <v>0.239747</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.245048</v>
+        <v>0.245079</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_9.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_4.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3879,7 +3879,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.23974</v>
+        <v>0.23975</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.245068</v>
+        <v>0.245067</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_18.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_0.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -3972,7 +3972,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.23975</v>
+        <v>0.239747</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0.245045</v>
+        <v>0.245062</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_2.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_13.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4065,43 +4065,35 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.188827</v>
+        <v>0.23975</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1790732256</v>
+        <v>1790732314</v>
       </c>
       <c r="E38" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="F38" t="n">
         <v>200000</v>
       </c>
-      <c r="G38" t="n">
-        <v>0.593838</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.664577</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.627219</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>0.187661</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.6</v>
-      </c>
+        <v>0.245045</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0.635294</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.617143</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>0.2</v>
       </c>
@@ -4136,23 +4128,23 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790732314_2.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z38" t="n">
         <v>15</v>
       </c>
       <c r="AA38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4166,7 +4158,7 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.186421</v>
+        <v>0.189742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4183,25 +4175,25 @@
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.57975</v>
+        <v>0.594828</v>
       </c>
       <c r="H39" t="n">
-        <v>0.655172</v>
+        <v>0.648903</v>
       </c>
       <c r="I39" t="n">
-        <v>0.615158</v>
+        <v>0.62069</v>
       </c>
       <c r="J39" t="n">
-        <v>0.187781</v>
+        <v>0.189614</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5672509999999999</v>
+        <v>0.5988019999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>0.570588</v>
+        <v>0.588235</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5689149999999999</v>
+        <v>0.593472</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4237,7 +4229,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_1.txt</t>
+          <t>_2_15_1_1790732256_10.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4267,7 +4259,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.184474</v>
+        <v>0.186589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4284,25 +4276,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.578729</v>
+        <v>0.599338</v>
       </c>
       <c r="H40" t="n">
-        <v>0.65674</v>
+        <v>0.567398</v>
       </c>
       <c r="I40" t="n">
-        <v>0.615272</v>
+        <v>0.582931</v>
       </c>
       <c r="J40" t="n">
-        <v>0.185581</v>
+        <v>0.184527</v>
       </c>
       <c r="K40" t="n">
-        <v>0.594595</v>
+        <v>0.605442</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6470590000000001</v>
+        <v>0.523529</v>
       </c>
       <c r="M40" t="n">
-        <v>0.619718</v>
+        <v>0.561514</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4338,7 +4330,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_15_1_1790732256_15.txt</t>
+          <t>_2_15_1_1790732256_3.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4368,35 +4360,43 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.239747</v>
+        <v>0.182785</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790732314</v>
+        <v>1790732256</v>
       </c>
       <c r="E41" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0.59584</v>
+      </c>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>0.6285269999999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.611747</v>
+      </c>
       <c r="J41" t="n">
-        <v>0.245064</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
+        <v>0.183844</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.601156</v>
+      </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.611765</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.606414</v>
+      </c>
       <c r="N41" t="n">
         <v>0.2</v>
       </c>
@@ -4431,23 +4431,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790732314_6.txt</t>
+          <t>_2_15_1_1790732256_8.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>15</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v>0.61305885</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03489064788777856</v>
+        <v>0.03489064788777858</v>
       </c>
       <c r="D2" t="n">
         <v>0.693182</v>
